--- a/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
+++ b/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure1\Rawdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A035BD-D453-41B6-AE01-8C14B2D03B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B41F52-0F87-47C5-B93D-200295944D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,10 +94,33 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,8 +146,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -413,7 +440,7 @@
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -446,8 +473,9 @@
       <c r="E2">
         <v>29.2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -463,8 +491,9 @@
       <c r="E3">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -480,8 +509,9 @@
       <c r="E4">
         <v>33.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -497,8 +527,9 @@
       <c r="E5">
         <v>32.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -514,8 +545,9 @@
       <c r="E6">
         <v>26.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -531,142 +563,151 @@
       <c r="E7">
         <v>28.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>29.8</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>31.6</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>31.5</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8">
+      <c r="B13" s="3">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="3">
         <v>29.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9">
+      <c r="B14" s="1">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="1">
         <v>30.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10">
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11">
-        <v>31.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12">
+      <c r="B15" s="2">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15">
-        <v>30</v>
-      </c>
+      <c r="F15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
+++ b/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure1\Rawdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B41F52-0F87-47C5-B93D-200295944D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFEFD7A-7B23-4B77-A7DA-FA0F30C3B695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13365" yWindow="4095" windowWidth="12690" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -88,6 +88,18 @@
   </si>
   <si>
     <t>572M4</t>
+  </si>
+  <si>
+    <t>1854_M3</t>
+  </si>
+  <si>
+    <t>1854_M2</t>
+  </si>
+  <si>
+    <t>1854_M5</t>
+  </si>
+  <si>
+    <t>1854_M4</t>
   </si>
 </sst>
 </file>
@@ -146,10 +158,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -432,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -473,7 +484,7 @@
       <c r="E2">
         <v>29.2</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -491,7 +502,7 @@
       <c r="E3">
         <v>28</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -509,7 +520,7 @@
       <c r="E4">
         <v>33.1</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -527,7 +538,7 @@
       <c r="E5">
         <v>32.5</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -545,7 +556,7 @@
       <c r="E6">
         <v>26.9</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -563,7 +574,7 @@
       <c r="E7">
         <v>28.3</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -581,7 +592,7 @@
       <c r="E8">
         <v>29.8</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -599,7 +610,7 @@
       <c r="E9">
         <v>31.6</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -617,7 +628,7 @@
       <c r="E10">
         <v>31.5</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -635,7 +646,7 @@
       <c r="E11">
         <v>29</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -653,25 +664,25 @@
       <c r="E12">
         <v>30</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="3">
-        <v>16</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="B13" s="2">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2">
         <v>29.3</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -691,23 +702,79 @@
       </c>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15">
         <v>33</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
+++ b/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure1\Rawdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFEFD7A-7B23-4B77-A7DA-FA0F30C3B695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F83EAA3-2E2F-43AA-9CA6-2E84A32CC345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13365" yWindow="4095" windowWidth="12690" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10200" yWindow="4095" windowWidth="12690" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -100,6 +100,18 @@
   </si>
   <si>
     <t>1854_M4</t>
+  </si>
+  <si>
+    <t>1855_M5</t>
+  </si>
+  <si>
+    <t>1855_M4</t>
+  </si>
+  <si>
+    <t>1855_M3</t>
+  </si>
+  <si>
+    <t>1855_M1</t>
   </si>
 </sst>
 </file>
@@ -443,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -733,8 +745,11 @@
       <c r="D16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -747,8 +762,11 @@
       <c r="D17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -761,8 +779,11 @@
       <c r="D18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -774,6 +795,77 @@
       </c>
       <c r="D19" t="s">
         <v>19</v>
+      </c>
+      <c r="E19">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23">
+        <v>24.8</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
+++ b/Data/Figure1/Rawdata/ChowMiceKeyPhotometry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure1\Rawdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F83EAA3-2E2F-43AA-9CA6-2E84A32CC345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90652301-D32A-4625-9A88-7B71EE03640E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10200" yWindow="4095" windowWidth="12690" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -90,28 +90,16 @@
     <t>572M4</t>
   </si>
   <si>
-    <t>1854_M3</t>
-  </si>
-  <si>
-    <t>1854_M2</t>
-  </si>
-  <si>
-    <t>1854_M5</t>
-  </si>
-  <si>
-    <t>1854_M4</t>
-  </si>
-  <si>
-    <t>1855_M5</t>
-  </si>
-  <si>
-    <t>1855_M4</t>
-  </si>
-  <si>
-    <t>1855_M3</t>
-  </si>
-  <si>
-    <t>1855_M1</t>
+    <t>1854M3</t>
+  </si>
+  <si>
+    <t>1854M2</t>
+  </si>
+  <si>
+    <t>1854M5</t>
+  </si>
+  <si>
+    <t>1854M4</t>
   </si>
 </sst>
 </file>
@@ -455,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -800,74 +788,6 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21">
-        <v>23.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23">
-        <v>24.8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
